--- a/diseases/d071/2026-2029.xlsx
+++ b/diseases/d071/2026-2029.xlsx
@@ -3639,6 +3639,402 @@
         </is>
       </c>
     </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>D071</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>unspecified-viral-hepatitis</t>
+        </is>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>Unspecified viral hepatitis</t>
+        </is>
+      </c>
+      <c r="E18" t="inlineStr">
+        <is>
+          <t>public_projection</t>
+        </is>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>CN</t>
+        </is>
+      </c>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>China</t>
+        </is>
+      </c>
+      <c r="H18" t="inlineStr">
+        <is>
+          <t>D071</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr">
+        <is>
+          <t>Unspecified viral hepatitis</t>
+        </is>
+      </c>
+      <c r="J18" t="inlineStr">
+        <is>
+          <t>未明示的病毒性肝炎</t>
+        </is>
+      </c>
+      <c r="K18" t="inlineStr">
+        <is>
+          <t>Viral</t>
+        </is>
+      </c>
+      <c r="L18" t="inlineStr">
+        <is>
+          <t>2026-08-01</t>
+        </is>
+      </c>
+      <c r="M18" t="inlineStr">
+        <is>
+          <t>2026-08</t>
+        </is>
+      </c>
+      <c r="N18" t="n">
+        <v>769</v>
+      </c>
+      <c r="O18" t="n">
+        <v>769</v>
+      </c>
+      <c r="Q18" t="n">
+        <v>0</v>
+      </c>
+      <c r="R18" t="n">
+        <v>0.05442652219685896</v>
+      </c>
+      <c r="S18" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
+      <c r="U18" t="inlineStr">
+        <is>
+          <t>SER_CN_UNSPECIFIED_VIRAL_HEPATITIS</t>
+        </is>
+      </c>
+      <c r="AA18" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
+      <c r="AO18" t="inlineStr">
+        <is>
+          <t>mixed</t>
+        </is>
+      </c>
+      <c r="AP18" t="inlineStr">
+        <is>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ18" t="inlineStr">
+        <is>
+          <t>legacy_gap_fill</t>
+        </is>
+      </c>
+      <c r="AS18" t="inlineStr">
+        <is>
+          <t>SER_CN_UNSPECIFIED_VIRAL_HEPATITIS</t>
+        </is>
+      </c>
+      <c r="AT18" t="n">
+        <v>1</v>
+      </c>
+      <c r="AU18" t="inlineStr">
+        <is>
+          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
+        </is>
+      </c>
+      <c r="AV18" t="inlineStr">
+        <is>
+          <t>cdc_weekly</t>
+        </is>
+      </c>
+      <c r="AW18" t="inlineStr">
+        <is>
+          <t>China CDC Weekly</t>
+        </is>
+      </c>
+      <c r="AX18" t="inlineStr">
+        <is>
+          <t>https://weekly.chinacdc.cn</t>
+        </is>
+      </c>
+      <c r="AY18" t="inlineStr">
+        <is>
+          <t>web</t>
+        </is>
+      </c>
+      <c r="AZ18" t="inlineStr">
+        <is>
+          <t>cdc_weekly; nhc; pubmed</t>
+        </is>
+      </c>
+      <c r="BA18" t="inlineStr">
+        <is>
+          <t>China CDC Weekly; National Disease Control and Prevention Administration; PubMed</t>
+        </is>
+      </c>
+      <c r="BB18" t="inlineStr">
+        <is>
+          <t>https://weekly.chinacdc.cn; https://www.ndcpa.gov.cn; https://pubmed.ncbi.nlm.nih.gov</t>
+        </is>
+      </c>
+      <c r="BC18" t="inlineStr">
+        <is>
+          <t>web; web; web</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>D071</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>unspecified-viral-hepatitis</t>
+        </is>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>Unspecified viral hepatitis</t>
+        </is>
+      </c>
+      <c r="E19" t="inlineStr">
+        <is>
+          <t>source_series_observation</t>
+        </is>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>CN</t>
+        </is>
+      </c>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>China</t>
+        </is>
+      </c>
+      <c r="H19" t="inlineStr">
+        <is>
+          <t>D071</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr">
+        <is>
+          <t>Unspecified viral hepatitis</t>
+        </is>
+      </c>
+      <c r="J19" t="inlineStr">
+        <is>
+          <t>未明示的病毒性肝炎</t>
+        </is>
+      </c>
+      <c r="K19" t="inlineStr">
+        <is>
+          <t>Viral</t>
+        </is>
+      </c>
+      <c r="L19" t="inlineStr">
+        <is>
+          <t>2026-08-01</t>
+        </is>
+      </c>
+      <c r="M19" t="inlineStr">
+        <is>
+          <t>2026-08</t>
+        </is>
+      </c>
+      <c r="N19" t="n">
+        <v>769</v>
+      </c>
+      <c r="O19" t="n">
+        <v>769</v>
+      </c>
+      <c r="U19" t="inlineStr">
+        <is>
+          <t>SER_CN_UNSPECIFIED_VIRAL_HEPATITIS</t>
+        </is>
+      </c>
+      <c r="V19" t="inlineStr">
+        <is>
+          <t>SER_CN_UNSPECIFIED_VIRAL_HEPATITIS</t>
+        </is>
+      </c>
+      <c r="W19" t="inlineStr">
+        <is>
+          <t>SRC_CN_CDC</t>
+        </is>
+      </c>
+      <c r="X19" t="inlineStr">
+        <is>
+          <t>未分型肝炎</t>
+        </is>
+      </c>
+      <c r="Y19" t="inlineStr">
+        <is>
+          <t>case_notifications</t>
+        </is>
+      </c>
+      <c r="Z19" t="inlineStr">
+        <is>
+          <t>notification</t>
+        </is>
+      </c>
+      <c r="AA19" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
+      <c r="AB19" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="AC19" t="inlineStr">
+        <is>
+          <t>country:CN:national</t>
+        </is>
+      </c>
+      <c r="AD19" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AE19" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="AF19" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
+      <c r="AG19" t="inlineStr">
+        <is>
+          <t>non_additive</t>
+        </is>
+      </c>
+      <c r="AH19" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="AI19" t="inlineStr">
+        <is>
+          <t>missing_is_unknown</t>
+        </is>
+      </c>
+      <c r="AJ19" t="inlineStr">
+        <is>
+          <t>globalid-disease-ontology:2026.08.30.1</t>
+        </is>
+      </c>
+      <c r="AK19" t="inlineStr">
+        <is>
+          <t>China CDC unclassified/unspecified viral hepatitis source category, including historical 'Other hepatitis' labels; migrated from legacy D012.</t>
+        </is>
+      </c>
+      <c r="AM19" t="inlineStr">
+        <is>
+          <t>raw</t>
+        </is>
+      </c>
+      <c r="AN19" t="b">
+        <v>1</v>
+      </c>
+      <c r="AO19" t="inlineStr">
+        <is>
+          <t>mixed</t>
+        </is>
+      </c>
+      <c r="AP19" t="inlineStr">
+        <is>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ19" t="inlineStr">
+        <is>
+          <t>legacy_gap_fill</t>
+        </is>
+      </c>
+      <c r="AS19" t="inlineStr">
+        <is>
+          <t>SER_CN_UNSPECIFIED_VIRAL_HEPATITIS</t>
+        </is>
+      </c>
+      <c r="AT19" t="n">
+        <v>1</v>
+      </c>
+      <c r="AU19" t="inlineStr">
+        <is>
+          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
+        </is>
+      </c>
+      <c r="AV19" t="inlineStr">
+        <is>
+          <t>cdc_weekly</t>
+        </is>
+      </c>
+      <c r="AW19" t="inlineStr">
+        <is>
+          <t>China CDC Weekly</t>
+        </is>
+      </c>
+      <c r="AX19" t="inlineStr">
+        <is>
+          <t>https://weekly.chinacdc.cn</t>
+        </is>
+      </c>
+      <c r="AY19" t="inlineStr">
+        <is>
+          <t>web</t>
+        </is>
+      </c>
+      <c r="AZ19" t="inlineStr">
+        <is>
+          <t>cdc_weekly; nhc; pubmed</t>
+        </is>
+      </c>
+      <c r="BA19" t="inlineStr">
+        <is>
+          <t>China CDC Weekly; National Disease Control and Prevention Administration; PubMed</t>
+        </is>
+      </c>
+      <c r="BB19" t="inlineStr">
+        <is>
+          <t>https://weekly.chinacdc.cn; https://www.ndcpa.gov.cn; https://pubmed.ncbi.nlm.nih.gov</t>
+        </is>
+      </c>
+      <c r="BC19" t="inlineStr">
+        <is>
+          <t>web; web; web</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -3672,7 +4068,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026-07-01</t>
+          <t>2026-08-01</t>
         </is>
       </c>
     </row>
@@ -3755,7 +4151,7 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
     </row>
     <row r="10">
@@ -3765,7 +4161,7 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>16</v>
+        <v>18</v>
       </c>
     </row>
     <row r="11">
@@ -3785,7 +4181,7 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
     </row>
     <row r="13">
@@ -3817,7 +4213,7 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>4137</v>
+        <v>4906</v>
       </c>
     </row>
     <row r="16">

--- a/diseases/d071/2026-2029.xlsx
+++ b/diseases/d071/2026-2029.xlsx
@@ -1166,7 +1166,7 @@
       </c>
       <c r="AJ4" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
         </is>
       </c>
       <c r="AK4" t="inlineStr">
@@ -1886,7 +1886,7 @@
       </c>
       <c r="AJ8" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
         </is>
       </c>
       <c r="AK8" t="inlineStr">
@@ -2441,7 +2441,7 @@
       </c>
       <c r="AJ11" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
         </is>
       </c>
       <c r="AK11" t="inlineStr">
@@ -2996,7 +2996,7 @@
       </c>
       <c r="AJ14" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
         </is>
       </c>
       <c r="AK14" t="inlineStr">
@@ -3554,7 +3554,7 @@
       </c>
       <c r="AJ17" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
         </is>
       </c>
       <c r="AK17" t="inlineStr">
@@ -3950,7 +3950,7 @@
       </c>
       <c r="AJ19" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
         </is>
       </c>
       <c r="AK19" t="inlineStr">

--- a/diseases/d071/2026-2029.xlsx
+++ b/diseases/d071/2026-2029.xlsx
@@ -1551,7 +1551,7 @@
       </c>
       <c r="AJ6" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.09.26.1</t>
+          <t>globalid-disease-ontology:2026.10.16.1</t>
         </is>
       </c>
       <c r="AK6" t="inlineStr">
@@ -2656,7 +2656,7 @@
       </c>
       <c r="AJ12" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.09.26.1</t>
+          <t>globalid-disease-ontology:2026.10.16.1</t>
         </is>
       </c>
       <c r="AK12" t="inlineStr">
@@ -3211,7 +3211,7 @@
       </c>
       <c r="AJ15" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.09.26.1</t>
+          <t>globalid-disease-ontology:2026.10.16.1</t>
         </is>
       </c>
       <c r="AK15" t="inlineStr">
@@ -4536,7 +4536,7 @@
       </c>
       <c r="AJ22" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.09.26.1</t>
+          <t>globalid-disease-ontology:2026.10.16.1</t>
         </is>
       </c>
       <c r="AK22" t="inlineStr">
